--- a/data/trans_orig/P15B_tráfico-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15B_tráfico-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21085</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>28285</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32482</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>28811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>22795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>32786</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>48799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20629</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>28238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29837</t>
+          <t>29570</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51001</t>
+          <t>50479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46981</t>
+          <t>46575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72619</t>
+          <t>72212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71019</t>
+          <t>71541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92183</t>
+          <t>92450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>81071</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>143206</t>
+          <t>143613</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>168844</t>
+          <t>169250</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30923</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14378</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24980</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43626</t>
+          <t>43779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25567</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>29646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49785</t>
+          <t>50440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45748</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62493</t>
+          <t>62757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30026</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41302</t>
+          <t>41646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65594</t>
+          <t>66246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81699</t>
+          <t>82623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>43810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>102653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122360</t>
+          <t>122491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42520</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53202</t>
+          <t>54065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71658</t>
+          <t>71445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86641</t>
+          <t>86587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>22929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71744</t>
+          <t>71872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84303</t>
+          <t>84463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90017</t>
+          <t>89666</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105422</t>
+          <t>105194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59210</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89346</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61910</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102019</t>
+          <t>103161</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141291</t>
+          <t>144262</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197626</t>
+          <t>197917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>227762</t>
+          <t>229550</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>193988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>219489</t>
+          <t>219925</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>401086</t>
+          <t>398115</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>440358</t>
+          <t>439216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29375</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>38753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34332</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>27303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36992</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>48904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33033</t>
+          <t>33127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60465</t>
+          <t>60726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79794</t>
+          <t>78363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11133</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30968</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>38698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63679</t>
+          <t>63718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75688</t>
+          <t>75568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44547</t>
+          <t>43844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55870</t>
+          <t>56219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66468</t>
+          <t>66228</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81268</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54840</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>61994</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>142929</t>
+          <t>141268</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166326</t>
+          <t>166166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147049</t>
+          <t>147234</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>167875</t>
+          <t>168338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>296984</t>
+          <t>297485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>328808</t>
+          <t>327229</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>22894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>32528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>44081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>16735</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36085</t>
+          <t>38899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50714</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20441</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>29197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>28216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>39822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25351</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>20057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37123</t>
+          <t>43367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>59819</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41138</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58974</t>
+          <t>67806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32530</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>49458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91678</t>
+          <t>103984</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>78870</t>
+          <t>89807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99682</t>
+          <t>113117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>29412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>32832</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>37379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>35671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>50603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>74445</t>
+          <t>78511</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63618</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80900</t>
+          <t>86200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>38630</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>43420</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31163</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51417</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>76058</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59698</t>
+          <t>64323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>108406</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82080</t>
+          <t>89035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121098</t>
+          <t>130838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>143695</t>
+          <t>157724</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126703</t>
+          <t>141023</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>157940</t>
+          <t>170710</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>162588</t>
+          <t>176363</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147938</t>
+          <t>161089</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>173402</t>
+          <t>187975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>306284</t>
+          <t>334086</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>283460</t>
+          <t>311654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>322478</t>
+          <t>353457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>196921</t>
+          <t>217081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>196921</t>
+          <t>217081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>196921</t>
+          <t>217081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>404558</t>
+          <t>442492</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>404558</t>
+          <t>442492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>404558</t>
+          <t>442492</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
